--- a/python/output/EPI.xlsx
+++ b/python/output/EPI.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D505"/>
+  <dimension ref="A1:D649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8509,6 +8509,2310 @@
         <v>6.0915679084702</v>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" s="1" t="n">
+        <v>1544</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D506" t="n">
+        <v>55.88390389514446</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="n">
+        <v>1547</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D507" t="n">
+        <v>40.09919572272855</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="n">
+        <v>1550</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D508" t="n">
+        <v>41.29543980549941</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="n">
+        <v>1551</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D509" t="n">
+        <v>51.25187269749058</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="n">
+        <v>1555</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>BGD</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D510" t="n">
+        <v>22.41683592293936</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="n">
+        <v>1557</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D511" t="n">
+        <v>45.75224462371848</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="n">
+        <v>1558</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D512" t="n">
+        <v>52.15840141737475</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="n">
+        <v>1566</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D513" t="n">
+        <v>43.73070106186491</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="n">
+        <v>1568</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D514" t="n">
+        <v>22.01854554435663</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="n">
+        <v>1569</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>BGR</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D515" t="n">
+        <v>52.09898550123203</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="n">
+        <v>1573</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>KHM</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D516" t="n">
+        <v>7.412172627111575</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="n">
+        <v>1574</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D517" t="n">
+        <v>30.6199993991508</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="n">
+        <v>1575</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D518" t="n">
+        <v>46.07875685027945</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="n">
+        <v>1579</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D519" t="n">
+        <v>38.20783863307766</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="n">
+        <v>1580</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D520" t="n">
+        <v>37.66725479487663</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="n">
+        <v>1581</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D521" t="n">
+        <v>31.76651885423124</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="n">
+        <v>1584</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D522" t="n">
+        <v>42.20201671153826</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="n">
+        <v>1585</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D523" t="n">
+        <v>27.28075326295608</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="n">
+        <v>1586</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>HRV</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D524" t="n">
+        <v>47.79687718965511</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="n">
+        <v>1589</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>CYP</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D525" t="n">
+        <v>40.8664363430517</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="n">
+        <v>1590</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D526" t="n">
+        <v>53.98863475628804</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="n">
+        <v>1591</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D527" t="n">
+        <v>24.69707111868302</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="n">
+        <v>1592</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>DNK</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D528" t="n">
+        <v>69.98453619300675</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="n">
+        <v>1597</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D529" t="n">
+        <v>37.58142456576725</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D530" t="n">
+        <v>80.76934382180012</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D531" t="n">
+        <v>63.9276703790162</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D532" t="n">
+        <v>63.95991058932458</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D533" t="n">
+        <v>63.95123748884641</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="n">
+        <v>1615</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D534" t="n">
+        <v>72.62718980327202</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="n">
+        <v>1627</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D535" t="n">
+        <v>42.30535909677566</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="n">
+        <v>1629</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D536" t="n">
+        <v>29.18887725133757</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="n">
+        <v>1630</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D537" t="n">
+        <v>25.11301108380716</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="n">
+        <v>1633</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D538" t="n">
+        <v>51.56335807159476</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="n">
+        <v>1635</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D539" t="n">
+        <v>48.48052617939025</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="n">
+        <v>1636</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D540" t="n">
+        <v>58.43209633155885</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="n">
+        <v>1638</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D541" t="n">
+        <v>63.03170854910144</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="n">
+        <v>1640</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>JOR</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D542" t="n">
+        <v>44.55237756625569</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="n">
+        <v>1641</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D543" t="n">
+        <v>33.54978312725463</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="n">
+        <v>1648</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>LVA</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D544" t="n">
+        <v>44.87867536279018</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="n">
+        <v>1654</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>LTU</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D545" t="n">
+        <v>46.89020277493927</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="n">
+        <v>1655</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>LUX</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D546" t="n">
+        <v>61.32630229182377</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="n">
+        <v>1659</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>MYS</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D547" t="n">
+        <v>33.91214098439382</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="n">
+        <v>1666</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D548" t="n">
+        <v>51.69875525967026</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D549" t="n">
+        <v>28.57187138096923</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>MMR</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D550" t="n">
+        <v>27.11646321660342</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="n">
+        <v>1678</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>NLD</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D551" t="n">
+        <v>60.03837939453074</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="n">
+        <v>1680</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D552" t="n">
+        <v>45.52039623337308</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="n">
+        <v>1683</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D553" t="n">
+        <v>40.82305527453276</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="n">
+        <v>1687</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D554" t="n">
+        <v>54.65208094941782</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>PAK</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D555" t="n">
+        <v>16.39910357115236</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="n">
+        <v>1694</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D556" t="n">
+        <v>32.5098112282575</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="n">
+        <v>1695</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D557" t="n">
+        <v>18.64203157493526</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="n">
+        <v>1696</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D558" t="n">
+        <v>47.49988585155023</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="n">
+        <v>1697</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D559" t="n">
+        <v>53.02208230644</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="n">
+        <v>1700</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D560" t="n">
+        <v>51.63076516870719</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D561" t="n">
+        <v>36.42024686872493</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="n">
+        <v>1710</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D562" t="n">
+        <v>17.82377687048048</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D563" t="n">
+        <v>38.25485000712778</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="n">
+        <v>1716</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D564" t="n">
+        <v>47.55515727683826</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="n">
+        <v>1717</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>SVN</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D565" t="n">
+        <v>55.82010217258778</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D566" t="n">
+        <v>43.37978821572</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="n">
+        <v>1721</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D567" t="n">
+        <v>44.43414613778332</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="n">
+        <v>1723</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D568" t="n">
+        <v>61.19777793673707</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="n">
+        <v>1729</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D569" t="n">
+        <v>67.41848645082047</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="n">
+        <v>1730</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D570" t="n">
+        <v>67.54813878617156</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="n">
+        <v>1735</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D571" t="n">
+        <v>43.16960613941468</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="n">
+        <v>1740</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D572" t="n">
+        <v>41.51999740317292</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="n">
+        <v>1741</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D573" t="n">
+        <v>29.56957129781463</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>UKR</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D574" t="n">
+        <v>49.97267862346178</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>1748</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D575" t="n">
+        <v>70.70887893947454</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="n">
+        <v>1749</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D576" t="n">
+        <v>49.57174483780749</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="n">
+        <v>1754</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D577" t="n">
+        <v>6.26465703383581</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="n">
+        <v>1764</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D578" t="n">
+        <v>53.98500861887385</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="n">
+        <v>1767</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D579" t="n">
+        <v>40.43621485515224</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="n">
+        <v>1770</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D580" t="n">
+        <v>42.38001849801395</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="n">
+        <v>1771</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D581" t="n">
+        <v>54.65341594319021</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="n">
+        <v>1775</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>BGD</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D582" t="n">
+        <v>24.22705960418562</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="n">
+        <v>1777</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D583" t="n">
+        <v>45.77353443670475</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="n">
+        <v>1778</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D584" t="n">
+        <v>54.7977173287256</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="n">
+        <v>1786</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D585" t="n">
+        <v>44.24411417804298</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="n">
+        <v>1788</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D586" t="n">
+        <v>16.54050058285863</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="n">
+        <v>1789</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>BGR</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D587" t="n">
+        <v>47.97374262395294</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="n">
+        <v>1793</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>KHM</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D588" t="n">
+        <v>8.316863414658654</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="n">
+        <v>1794</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D589" t="n">
+        <v>35.61553472069843</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="n">
+        <v>1795</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D590" t="n">
+        <v>47.30111493588003</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="n">
+        <v>1799</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D591" t="n">
+        <v>37.70587214650388</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="n">
+        <v>1800</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D592" t="n">
+        <v>35.20552861749889</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D593" t="n">
+        <v>35.2214909206582</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D594" t="n">
+        <v>43.10055376112459</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D595" t="n">
+        <v>25.92749306393144</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>HRV</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D596" t="n">
+        <v>47.88865593459998</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>CYP</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D597" t="n">
+        <v>40.33790119067678</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="n">
+        <v>1810</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D598" t="n">
+        <v>54.44475310175186</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D599" t="n">
+        <v>22.83124522396009</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="n">
+        <v>1812</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>DNK</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D600" t="n">
+        <v>71.56503940187041</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="n">
+        <v>1817</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D601" t="n">
+        <v>39.79638905443983</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="n">
+        <v>1821</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D602" t="n">
+        <v>83.35614233643665</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>1827</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D603" t="n">
+        <v>63.48202415590783</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>1828</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D604" t="n">
+        <v>65.85809168197574</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>1833</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D605" t="n">
+        <v>65.96211598417818</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>1835</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D606" t="n">
+        <v>71.43372704071956</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="n">
+        <v>1847</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D607" t="n">
+        <v>44.96519152106324</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="n">
+        <v>1849</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D608" t="n">
+        <v>29.46448534621524</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D609" t="n">
+        <v>19.54747108239932</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>1853</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D610" t="n">
+        <v>54.95731417284282</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>1855</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D611" t="n">
+        <v>42.18676047633562</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="n">
+        <v>1856</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D612" t="n">
+        <v>55.69670267837731</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="n">
+        <v>1858</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D613" t="n">
+        <v>63.32963607731261</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>1860</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>JOR</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D614" t="n">
+        <v>46.32313436332261</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="n">
+        <v>1861</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D615" t="n">
+        <v>38.39864127274738</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="n">
+        <v>1868</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>LVA</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D616" t="n">
+        <v>47.4174437612007</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="n">
+        <v>1874</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>LTU</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D617" t="n">
+        <v>49.00362360883526</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="n">
+        <v>1875</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>LUX</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D618" t="n">
+        <v>67.35900183401971</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="n">
+        <v>1879</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>MYS</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D619" t="n">
+        <v>36.76693420825349</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="n">
+        <v>1886</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D620" t="n">
+        <v>50.8962164488799</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="n">
+        <v>1892</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D621" t="n">
+        <v>28.23116460910764</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="n">
+        <v>1894</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>MMR</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D622" t="n">
+        <v>30.25451652513438</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="n">
+        <v>1898</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>NLD</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D623" t="n">
+        <v>65.13905339689116</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D624" t="n">
+        <v>47.71062726262327</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D625" t="n">
+        <v>41.43013877171924</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D626" t="n">
+        <v>56.81340872439466</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>PAK</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D627" t="n">
+        <v>18.41650617020683</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="n">
+        <v>1914</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D628" t="n">
+        <v>30.71511210218111</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="n">
+        <v>1915</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D629" t="n">
+        <v>21.55683077103583</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="n">
+        <v>1916</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D630" t="n">
+        <v>48.23382798401243</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="n">
+        <v>1917</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D631" t="n">
+        <v>57.56365079081588</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D632" t="n">
+        <v>50.4723965958292</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="n">
+        <v>1921</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D633" t="n">
+        <v>35.34180326651755</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="n">
+        <v>1930</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D634" t="n">
+        <v>17.33973953321456</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D635" t="n">
+        <v>43.26511621229868</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="n">
+        <v>1936</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D636" t="n">
+        <v>49.44417457487233</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="n">
+        <v>1937</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>SVN</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D637" t="n">
+        <v>56.00083225215852</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D638" t="n">
+        <v>45.39497957021641</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="n">
+        <v>1941</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D639" t="n">
+        <v>46.00332201641235</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D640" t="n">
+        <v>60.74335970132011</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="n">
+        <v>1949</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D641" t="n">
+        <v>67.86671663649814</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D642" t="n">
+        <v>68.83562898104907</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="n">
+        <v>1955</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D643" t="n">
+        <v>44.11212086587549</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D644" t="n">
+        <v>42.77688934880923</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D645" t="n">
+        <v>29.67760259813136</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>UKR</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D646" t="n">
+        <v>52.39452245144286</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D647" t="n">
+        <v>72.4922905412772</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D648" t="n">
+        <v>49.87474108136441</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D649" t="n">
+        <v>8.113896481380516</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/python/output/EPI.xlsx
+++ b/python/output/EPI.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D649"/>
+  <dimension ref="A1:D721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10813,6 +10813,1158 @@
         <v>8.113896481380516</v>
       </c>
     </row>
+    <row r="650">
+      <c r="A650" s="1" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D650" t="n">
+        <v>54.51911830477204</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D651" t="n">
+        <v>41.27054920420807</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D652" t="n">
+        <v>42.34769729536414</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D653" t="n">
+        <v>59.19410158979095</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>BGD</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D654" t="n">
+        <v>27.25263780019683</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D655" t="n">
+        <v>46.58096662653957</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D656" t="n">
+        <v>57.95818988862573</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D657" t="n">
+        <v>43.45987059526524</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D658" t="n">
+        <v>16.04986880430373</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>BGR</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D659" t="n">
+        <v>57.54652043656726</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>KHM</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D660" t="n">
+        <v>9.910419496119077</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D661" t="n">
+        <v>41.09729814827335</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D662" t="n">
+        <v>47.60571942975555</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D663" t="n">
+        <v>40.3575896244369</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D664" t="n">
+        <v>31.72781528766114</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D665" t="n">
+        <v>36.8413404015722</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D666" t="n">
+        <v>39.67451601784482</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D667" t="n">
+        <v>24.40304093389894</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>HRV</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D668" t="n">
+        <v>46.70067278653079</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>CYP</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D669" t="n">
+        <v>43.00937540006308</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D670" t="n">
+        <v>59.83567455690013</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D671" t="n">
+        <v>18.10637796646672</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>DNK</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D672" t="n">
+        <v>70.39332673604316</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D673" t="n">
+        <v>41.85784660607219</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D674" t="n">
+        <v>88.5867858143131</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="n">
+        <v>2047</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D675" t="n">
+        <v>64.54776020775998</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D676" t="n">
+        <v>69.2407163128684</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="n">
+        <v>2053</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D677" t="n">
+        <v>69.87691876259629</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="n">
+        <v>2055</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D678" t="n">
+        <v>73.17470753949041</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="n">
+        <v>2067</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D679" t="n">
+        <v>52.11214598418704</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="n">
+        <v>2069</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D680" t="n">
+        <v>29.11754400254469</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="n">
+        <v>2070</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D681" t="n">
+        <v>17.85796564278864</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="n">
+        <v>2073</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D682" t="n">
+        <v>59.89318257108707</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="n">
+        <v>2075</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D683" t="n">
+        <v>43.81696725970795</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n">
+        <v>2076</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D684" t="n">
+        <v>58.24983699057005</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n">
+        <v>2078</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D685" t="n">
+        <v>62.80537821102061</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="n">
+        <v>2080</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>JOR</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D686" t="n">
+        <v>47.76665340862069</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="n">
+        <v>2081</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D687" t="n">
+        <v>43.10245341090508</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="n">
+        <v>2088</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>LVA</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D688" t="n">
+        <v>50.39388695878473</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="n">
+        <v>2094</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>LTU</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D689" t="n">
+        <v>53.90353850408658</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="n">
+        <v>2095</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>LUX</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D690" t="n">
+        <v>72.32602015874475</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="n">
+        <v>2099</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>MYS</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D691" t="n">
+        <v>37.1488375709207</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="n">
+        <v>2106</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D692" t="n">
+        <v>49.49331693309387</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="n">
+        <v>2112</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D693" t="n">
+        <v>29.52477787493246</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="n">
+        <v>2114</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>MMR</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D694" t="n">
+        <v>35.36813235518488</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="n">
+        <v>2118</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>NLD</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D695" t="n">
+        <v>70.05175657451579</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="n">
+        <v>2120</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D696" t="n">
+        <v>50.56580304269923</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="n">
+        <v>2123</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D697" t="n">
+        <v>40.92980959009903</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="n">
+        <v>2127</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D698" t="n">
+        <v>59.44339789201324</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="n">
+        <v>2129</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>PAK</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D699" t="n">
+        <v>23.58516909634908</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="n">
+        <v>2134</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D700" t="n">
+        <v>31.38421093057814</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="n">
+        <v>2135</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D701" t="n">
+        <v>23.62670099342072</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="n">
+        <v>2136</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D702" t="n">
+        <v>52.72792271329478</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="n">
+        <v>2137</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D703" t="n">
+        <v>64.5101357476114</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="n">
+        <v>2140</v>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D704" t="n">
+        <v>54.91400729200458</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="n">
+        <v>2141</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D705" t="n">
+        <v>34.79961330699081</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D706" t="n">
+        <v>19.35342786918275</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="n">
+        <v>2154</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D707" t="n">
+        <v>43.95616439383488</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="n">
+        <v>2156</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D708" t="n">
+        <v>51.45832936848557</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="n">
+        <v>2157</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>SVN</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D709" t="n">
+        <v>57.67690694491113</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="n">
+        <v>2160</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D710" t="n">
+        <v>46.07220267561368</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="n">
+        <v>2161</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D711" t="n">
+        <v>48.18007536855774</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="n">
+        <v>2163</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D712" t="n">
+        <v>65.84088077654472</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="n">
+        <v>2169</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D713" t="n">
+        <v>68.05764973908356</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="n">
+        <v>2170</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D714" t="n">
+        <v>68.55425142954678</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="n">
+        <v>2175</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D715" t="n">
+        <v>45.76464806804826</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="n">
+        <v>2180</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D716" t="n">
+        <v>43.32728763305656</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="n">
+        <v>2181</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D717" t="n">
+        <v>30.00691039474407</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="n">
+        <v>2186</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>UKR</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D718" t="n">
+        <v>53.18175299904549</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="n">
+        <v>2188</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D719" t="n">
+        <v>72.05966118643163</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="n">
+        <v>2189</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D720" t="n">
+        <v>49.84551465174541</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="n">
+        <v>2194</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D721" t="n">
+        <v>11.24047419787707</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
